--- a/web/files/九龙-红磡-首汇.xlsx
+++ b/web/files/九龙-红磡-首汇.xlsx
@@ -6204,38 +6204,30 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>16030000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>26717</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K89" s="5" t="n">
+        <v>16030000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>26717</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6244,7 +6236,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15931,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -15949,7 +15941,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -16689,12 +16681,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
+$1603万
+$26,717/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-首汇.xlsx
+++ b/web/files/九龙-红磡-首汇.xlsx
@@ -10986,38 +10986,30 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I166" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>15010000</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>25017</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L166" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K166" s="5" t="n">
+        <v>15010000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>25017</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -11026,7 +11018,7 @@
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15931,7 +15923,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -15941,7 +15933,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17346,12 +17338,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
+$1501万
+$25,017/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-首汇.xlsx
+++ b/web/files/九龙-红磡-首汇.xlsx
@@ -6209,7 +6209,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -16678,7 +16678,7 @@
           <t>A | 600呎 (4+房)
 $1603万
 $26,717/呎
-(26年-09月-07日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-首汇.xlsx
+++ b/web/files/九龙-红磡-首汇.xlsx
@@ -10991,7 +10991,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -17343,7 +17343,7 @@
           <t>A | 600呎 (4+房)
 $1501万
 $25,017/呎
-(26年-09月-16日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-首汇.xlsx
+++ b/web/files/九龙-红磡-首汇.xlsx
@@ -15490,38 +15490,30 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>6641000</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>29000</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K238" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L238" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K238" s="5" t="n">
+        <v>6641000</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>29000</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -15530,7 +15522,7 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15915,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -15933,7 +15925,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18043,12 +18035,12 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 229呎 (1房)
-招标单位
--
-(在售)</t>
+$664万
+$29,000/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">

--- a/web/files/九龙-红磡-首汇.xlsx
+++ b/web/files/九龙-红磡-首汇.xlsx
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -18040,7 +18040,7 @@
           <t>F | 229呎 (1房)
 $664万
 $29,000/呎
-(26年-10月-12日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
